--- a/marketer_forms/010_user_persona_survey--marketer_forms.xlsx
+++ b/marketer_forms/010_user_persona_survey--marketer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user_persona_survey_form</t>
+          <t>marketer_forms_role</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>User Persona Survey</t>
+          <t>What is your role in the organization?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>user_persona_survey_category</t>
+          <t>marketer_forms_experience</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>What is your level of experience with marketing tools?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>user_persona_survey_description</t>
+          <t>marketer_forms_automation_tools_use</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>How do you currently use marketing automation tools?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>user_persona_survey_output_file</t>
+          <t>marketer_forms_communication_preferred</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>What is your preferred way of communication?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>user_persona_survey_assigned_tool</t>
+          <t>marketer_forms_experience_years</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>How many years do you have in experience with marketing software?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>user_persona_survey_form_ids</t>
+          <t>marketer_forms_goal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>What is your primary goal when using marketing automation tools?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>user_persona_survey_category_2</t>
+          <t>marketer_forms_pain_points</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Can you describe your current pain points when using marketing automation tools?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>user_persona_survey_description_2</t>
+          <t>marketer_forms_device_preferred</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Do you prefer using desktop or mobile apps for marketing automation?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>user_persona_survey_assigned_tool_2</t>
+          <t>marketer_forms_features</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Which features are most important to you when using marketing automation tools?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,21 +722,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>user_persona_survey_form_ids_2</t>
+          <t>marketer_forms_age_range</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>What is your age range?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>marketer_forms_job_title</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>What is your job title?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>marketer_forms_education</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>What is your highest level of education completed?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -753,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -781,66 +827,610 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>user_persona_survey_category_choices</t>
+          <t>marketer_forms_role_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>marketer_forms</t>
+          <t>marketing_manager</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Marketer Forms</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>user_persona_survey_category_choices</t>
+          <t>marketer_forms_role_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>sales_manager</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Sales Manager</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>user_persona_survey_category_2_choices</t>
+          <t>marketer_forms_role_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>marketer_forms</t>
+          <t>product_manager</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Marketer Forms</t>
+          <t>Product Manager</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>user_persona_survey_category_2_choices</t>
+          <t>marketer_forms_role_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>it_manager</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>IT Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>marketer_forms_role_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>other</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>marketer_forms_experience_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>marketer_forms_experience_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>intermediate</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>marketer_forms_experience_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>advanced</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Advanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>marketer_forms_experience_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Expert</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>marketer_forms_automation_tools_use_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>social_media_automation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Social media automation</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>marketer_forms_automation_tools_use_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>email_marketing</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Email marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>marketer_forms_automation_tools_use_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>content_creation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Content creation</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>marketer_forms_automation_tools_use_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>lead_generation</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Lead generation</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>marketer_forms_automation_tools_use_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>marketer_forms_communication_preferred_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>marketer_forms_communication_preferred_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>phone_call</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Phone call</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>marketer_forms_communication_preferred_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>messaging_app</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Messaging app</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>marketer_forms_communication_preferred_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>video_call</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Video call</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>marketer_forms_communication_preferred_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>in-person_meeting</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>In-person meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>marketer_forms_device_preferred_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>desktop</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>marketer_forms_device_preferred_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>marketer_forms_features_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>personalization</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Personalization</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>marketer_forms_features_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>marketer_forms_features_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>marketer_forms_features_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>reporting</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>marketer_forms_features_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>marketer_forms_age_range_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>18-24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>18-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>marketer_forms_age_range_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>25-34</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>marketer_forms_age_range_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>35-44</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>35-44</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>marketer_forms_age_range_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>45-54</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>45-54</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>marketer_forms_age_range_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>55+</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>55+</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>marketer_forms_education_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>high_school</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>High school</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>marketer_forms_education_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>bachelor's_degree</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>marketer_forms_education_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>master's_degree</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>marketer_forms_education_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>doctoral_degree</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Doctoral degree</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>marketer_forms_education_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
